--- a/servers/maze_main_server/conf.d/data/maze_excel_test_v8【迷宫-导表-测试】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_excel_test_v8【迷宫-导表-测试】.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
-    <sheet name="maze_level_v8" sheetId="1" r:id="rId1"/>
+    <sheet name="maze_excel_test_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="171">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -504,9 +504,6 @@
   </si>
   <si>
     <t>3010101:66037_3020101:13207_3030101:1056592_9101:264148</t>
-  </si>
-  <si>
-    <t>abc</t>
   </si>
   <si>
     <t>3010101:71426_3020101:14285_3030101:1142808_9101:285702</t>
@@ -555,7 +552,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -568,13 +565,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1024,148 +1014,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3616,8 +3606,8 @@
       <c r="B152" s="1">
         <v>58000</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>159</v>
+      <c r="C152" s="1">
+        <v>4293530</v>
       </c>
       <c r="D152" s="1">
         <v>0</v>
@@ -3634,7 +3624,7 @@
         <v>4293530</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3648,7 +3638,7 @@
         <v>4352330</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3662,7 +3652,7 @@
         <v>4411530</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3676,7 +3666,7 @@
         <v>4471130</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3690,7 +3680,7 @@
         <v>4531130</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3704,7 +3694,7 @@
         <v>4591530</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3718,7 +3708,7 @@
         <v>4652330</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3732,7 +3722,7 @@
         <v>4713530</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3746,7 +3736,7 @@
         <v>4775130</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3760,7 +3750,7 @@
         <v>4837130</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3774,7 +3764,7 @@
         <v>4899530</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3788,7 +3778,7 @@
         <v>4899530</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_excel_test_v8【迷宫-导表-测试】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_excel_test_v8【迷宫-导表-测试】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowHeight="16160"/>
   </bookViews>
   <sheets>
     <sheet name="maze_excel_test_v8" sheetId="1" r:id="rId1"/>
@@ -3769,7 +3769,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="1">
-        <v>160.2</v>
+        <v>160</v>
       </c>
       <c r="B164" s="1">
         <v>-1</v>

--- a/servers/maze_main_server/conf.d/data/maze_excel_test_v8【迷宫-导表-测试】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_excel_test_v8【迷宫-导表-测试】.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="169">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -521,13 +521,7 @@
     <t>3010101:88379_3020101:17676_3030101:1414056_9101:353514</t>
   </si>
   <si>
-    <t>3010101:91914_3020101:18383_3030101:1470616_9101:367654</t>
-  </si>
-  <si>
-    <t>3010101:95590_3020101:19118_3030101:1529440_9101:382360</t>
-  </si>
-  <si>
-    <t>3010101:99414_3020101:19883_3030101:1590616_9101:397654</t>
+    <t>01</t>
   </si>
   <si>
     <t>3010101:103390_3020101:20678_3030101:1654240_9101:413560</t>
@@ -3609,8 +3603,8 @@
       <c r="C152" s="1">
         <v>4293530</v>
       </c>
-      <c r="D152" s="1">
-        <v>0</v>
+      <c r="D152" s="2" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3707,8 +3701,8 @@
       <c r="C159" s="1">
         <v>4652330</v>
       </c>
-      <c r="D159" s="2" t="s">
-        <v>165</v>
+      <c r="D159" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3721,8 +3715,8 @@
       <c r="C160" s="1">
         <v>4713530</v>
       </c>
-      <c r="D160" s="2" t="s">
-        <v>166</v>
+      <c r="D160" s="1">
+        <v>123</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3736,7 +3730,7 @@
         <v>4775130</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3750,7 +3744,7 @@
         <v>4837130</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3764,7 +3758,7 @@
         <v>4899530</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3778,7 +3772,7 @@
         <v>4899530</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_excel_test_v8【迷宫-导表-测试】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_excel_test_v8【迷宫-导表-测试】.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="168">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -519,9 +519,6 @@
   </si>
   <si>
     <t>3010101:88379_3020101:17676_3030101:1414056_9101:353514</t>
-  </si>
-  <si>
-    <t>01</t>
   </si>
   <si>
     <t>3010101:103390_3020101:20678_3030101:1654240_9101:413560</t>
@@ -3688,7 +3685,7 @@
         <v>4591530</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3702,7 +3699,7 @@
         <v>4652330</v>
       </c>
       <c r="D159" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3715,8 +3712,8 @@
       <c r="C160" s="1">
         <v>4713530</v>
       </c>
-      <c r="D160" s="1">
-        <v>123</v>
+      <c r="D160" s="2" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3730,7 +3727,7 @@
         <v>4775130</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3744,7 +3741,7 @@
         <v>4837130</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3758,7 +3755,7 @@
         <v>4899530</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3772,7 +3769,7 @@
         <v>4899530</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_excel_test_v8【迷宫-导表-测试】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_excel_test_v8【迷宫-导表-测试】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="14160"/>
+    <workbookView windowHeight="16160"/>
   </bookViews>
   <sheets>
     <sheet name="maze_excel_test_v8" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="168">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3698,8 +3698,8 @@
       <c r="C159" s="1">
         <v>4652330</v>
       </c>
-      <c r="D159" s="2" t="s">
-        <v>164</v>
+      <c r="D159" s="1">
+        <v>0.1</v>
       </c>
     </row>
     <row r="160" spans="1:4">

--- a/servers/maze_main_server/conf.d/data/maze_excel_test_v8【迷宫-导表-测试】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_excel_test_v8【迷宫-导表-测试】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16160"/>
+    <workbookView windowHeight="14160"/>
   </bookViews>
   <sheets>
     <sheet name="maze_excel_test_v8" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="168">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3698,8 +3698,8 @@
       <c r="C159" s="1">
         <v>4652330</v>
       </c>
-      <c r="D159" s="1">
-        <v>0.1</v>
+      <c r="D159" s="2" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="160" spans="1:4">
